--- a/data/trans_dic/P36$cafe-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,37; 96,52</t>
+          <t>93,49; 96,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,82; 95,38</t>
+          <t>91,72; 95,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,39; 91,42</t>
+          <t>86,41; 91,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,54; 95,9</t>
+          <t>92,59; 95,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,11; 96,53</t>
+          <t>93,13; 96,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,29; 96,49</t>
+          <t>93,39; 96,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,48; 95,77</t>
+          <t>93,42; 95,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92,9; 95,51</t>
+          <t>92,92; 95,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90,45; 93,56</t>
+          <t>90,44; 93,31</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,84; 95,01</t>
+          <t>91,82; 95,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,74; 94,29</t>
+          <t>90,74; 94,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,09; 91,11</t>
+          <t>87,04; 91,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,64; 94,02</t>
+          <t>90,64; 94,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,6; 95,62</t>
+          <t>92,59; 95,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,6; 93,16</t>
+          <t>89,65; 93,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,74; 94,04</t>
+          <t>91,73; 94,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,08; 94,37</t>
+          <t>92,21; 94,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,22; 91,75</t>
+          <t>89,05; 91,76</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,77; 91,72</t>
+          <t>86,66; 91,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,41; 90,41</t>
+          <t>85,38; 90,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,5; 93,76</t>
+          <t>89,77; 93,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,94; 93,06</t>
+          <t>88,64; 93,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,15; 93,48</t>
+          <t>89,35; 93,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,55; 95,81</t>
+          <t>92,49; 95,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,59; 91,98</t>
+          <t>88,6; 91,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88,09; 91,31</t>
+          <t>88,22; 91,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,8; 94,42</t>
+          <t>91,93; 94,37</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,09; 90,26</t>
+          <t>86,23; 90,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,22; 93,05</t>
+          <t>89,19; 92,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,15; 94,55</t>
+          <t>91,18; 94,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,2; 91,0</t>
+          <t>87,21; 91,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,06; 95,15</t>
+          <t>92,09; 95,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,4; 95,4</t>
+          <t>92,56; 95,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,34; 90,07</t>
+          <t>87,36; 90,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,24; 93,64</t>
+          <t>91,19; 93,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,52; 94,7</t>
+          <t>92,33; 94,69</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,48; 92,43</t>
+          <t>90,33; 92,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,44; 92,4</t>
+          <t>90,49; 92,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,7; 91,82</t>
+          <t>89,74; 91,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,66; 92,53</t>
+          <t>90,53; 92,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,69; 94,4</t>
+          <t>92,72; 94,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,74; 94,38</t>
+          <t>92,74; 94,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,89; 92,16</t>
+          <t>90,79; 92,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91,92; 93,2</t>
+          <t>91,89; 93,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91,51; 92,85</t>
+          <t>91,62; 92,88</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,...</t>
+          <t>Población que desayuna, al menos, café, leche, té, chololate, yogurt,... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>647102; 668901</t>
+          <t>647883; 670348</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>644113; 669076</t>
+          <t>643422; 670123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>581437; 615281</t>
+          <t>581553; 613756</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>637002; 660119</t>
+          <t>637357; 659703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>648157; 671962</t>
+          <t>648314; 672049</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>626599; 648073</t>
+          <t>627279; 649045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1291313; 1322965</t>
+          <t>1290482; 1324704</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1298322; 1334811</t>
+          <t>1298687; 1335481</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1216253; 1258039</t>
+          <t>1216175; 1254672</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>880656; 911031</t>
+          <t>880462; 911005</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>923645; 959808</t>
+          <t>923711; 959009</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>889497; 930492</t>
+          <t>888914; 930405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>876867; 909543</t>
+          <t>876817; 909974</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>953894; 984959</t>
+          <t>953810; 985088</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>933602; 970692</t>
+          <t>934161; 969336</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1767103; 1811441</t>
+          <t>1766987; 1813875</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1885861; 1932788</t>
+          <t>1888461; 1935867</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1840910; 1893102</t>
+          <t>1837416; 1893235</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>587845; 621383</t>
+          <t>587091; 620300</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645367; 683171</t>
+          <t>645103; 683389</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>678828; 711151</t>
+          <t>680877; 712257</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>608220; 636368</t>
+          <t>606141; 636122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>691934; 725593</t>
+          <t>693515; 724809</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>726539; 752095</t>
+          <t>726056; 751210</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1205971; 1252153</t>
+          <t>1206095; 1248937</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1349263; 1398718</t>
+          <t>1351320; 1400574</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1416944; 1457344</t>
+          <t>1418973; 1456523</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>809633; 848879</t>
+          <t>810976; 848838</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>843872; 880106</t>
+          <t>843612; 879116</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>854575; 886481</t>
+          <t>854895; 886518</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>903036; 942375</t>
+          <t>903095; 943984</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>966435; 998832</t>
+          <t>966769; 997332</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>963457; 994754</t>
+          <t>965057; 995770</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1725828; 1779789</t>
+          <t>1726282; 1781334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1820812; 1868714</t>
+          <t>1819880; 1868781</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1832161; 1875193</t>
+          <t>1828401; 1875153</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2958647; 3022335</t>
+          <t>2953472; 3020686</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3093794; 3160962</t>
+          <t>3095519; 3160006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3041234; 3112948</t>
+          <t>3042692; 3113510</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3060053; 3122923</t>
+          <t>3055452; 3122071</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3292647; 3353261</t>
+          <t>3293620; 3348714</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3284294; 3342354</t>
+          <t>3284043; 3342862</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6039320; 6124212</t>
+          <t>6033195; 6125749</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6409528; 6498596</t>
+          <t>6407334; 6499895</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6343469; 6435749</t>
+          <t>6350672; 6437806</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$cafe-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$cafe-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,49; 96,73</t>
+          <t>93,3; 96,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>91,72; 95,53</t>
+          <t>91,53; 95,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,41; 91,19</t>
+          <t>86,34; 91,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,59; 95,84</t>
+          <t>92,4; 95,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,13; 96,54</t>
+          <t>93,23; 96,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,39; 96,64</t>
+          <t>93,4; 96,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,42; 95,9</t>
+          <t>93,58; 95,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>92,92; 95,56</t>
+          <t>93,16; 95,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90,44; 93,31</t>
+          <t>90,43; 93,51</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,82; 95,01</t>
+          <t>91,87; 95,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90,74; 94,21</t>
+          <t>90,82; 94,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,04; 91,1</t>
+          <t>87,16; 91,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,64; 94,06</t>
+          <t>90,43; 94,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,59; 95,63</t>
+          <t>92,56; 95,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,65; 93,03</t>
+          <t>89,8; 93,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,73; 94,17</t>
+          <t>91,67; 94,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,21; 94,52</t>
+          <t>92,22; 94,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,05; 91,76</t>
+          <t>89,0; 91,66</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,66; 91,56</t>
+          <t>86,91; 91,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,38; 90,44</t>
+          <t>85,69; 90,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,77; 93,91</t>
+          <t>89,62; 93,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,64; 93,02</t>
+          <t>88,56; 92,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,35; 93,38</t>
+          <t>89,24; 93,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>92,49; 95,69</t>
+          <t>92,51; 95,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,6; 91,75</t>
+          <t>88,51; 91,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88,22; 91,43</t>
+          <t>88,26; 91,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91,93; 94,37</t>
+          <t>91,55; 94,23</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,23; 90,26</t>
+          <t>86,12; 90,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,19; 92,94</t>
+          <t>88,91; 92,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,18; 94,56</t>
+          <t>91,02; 94,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,21; 91,15</t>
+          <t>87,16; 91,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,09; 95,0</t>
+          <t>92,06; 95,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,56; 95,5</t>
+          <t>92,48; 95,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,36; 90,15</t>
+          <t>87,2; 90,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,19; 93,64</t>
+          <t>91,18; 93,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,33; 94,69</t>
+          <t>92,33; 94,61</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,33; 92,38</t>
+          <t>90,49; 92,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,49; 92,37</t>
+          <t>90,41; 92,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,74; 91,83</t>
+          <t>89,73; 91,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,5</t>
+          <t>90,57; 92,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,72; 94,27</t>
+          <t>92,69; 94,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,74; 94,4</t>
+          <t>92,65; 94,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,79; 92,19</t>
+          <t>90,89; 92,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>91,89; 93,21</t>
+          <t>91,89; 93,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91,62; 92,88</t>
+          <t>91,64; 92,88</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>647883; 670348</t>
+          <t>646570; 669481</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>643422; 670123</t>
+          <t>642050; 670109</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>581553; 613756</t>
+          <t>581110; 613935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>637357; 659703</t>
+          <t>636060; 659573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>648314; 672049</t>
+          <t>648958; 672556</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>627279; 649045</t>
+          <t>627297; 649933</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1290482; 1324704</t>
+          <t>1292671; 1323904</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1298687; 1335481</t>
+          <t>1302031; 1337534</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1216175; 1254672</t>
+          <t>1215961; 1257350</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>880462; 911005</t>
+          <t>880862; 911302</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>923711; 959009</t>
+          <t>924489; 959328</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>888914; 930405</t>
+          <t>890220; 931662</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>876817; 909974</t>
+          <t>874821; 910512</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>953810; 985088</t>
+          <t>953497; 986034</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>934161; 969336</t>
+          <t>935668; 970857</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1766987; 1813875</t>
+          <t>1765875; 1811546</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1888461; 1935867</t>
+          <t>1888738; 1935478</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1837416; 1893235</t>
+          <t>1836373; 1891306</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>587091; 620300</t>
+          <t>588812; 620398</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645103; 683389</t>
+          <t>647486; 683094</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>680877; 712257</t>
+          <t>679732; 710925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>606141; 636122</t>
+          <t>605634; 635292</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>693515; 724809</t>
+          <t>692630; 724627</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>726056; 751210</t>
+          <t>726230; 752358</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1206095; 1248937</t>
+          <t>1204899; 1250250</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1351320; 1400574</t>
+          <t>1352008; 1399959</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1418973; 1456523</t>
+          <t>1413012; 1454380</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>810976; 848838</t>
+          <t>809871; 848311</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>843612; 879116</t>
+          <t>840943; 878274</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>854895; 886518</t>
+          <t>853404; 885480</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>903095; 943984</t>
+          <t>902624; 943479</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>966769; 997332</t>
+          <t>966467; 997580</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>965057; 995770</t>
+          <t>964231; 995257</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1726282; 1781334</t>
+          <t>1723107; 1780663</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1819880; 1868781</t>
+          <t>1819587; 1866881</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1828401; 1875153</t>
+          <t>1828350; 1873527</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2953472; 3020686</t>
+          <t>2958997; 3023394</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3095519; 3160006</t>
+          <t>3092777; 3162417</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3042692; 3113510</t>
+          <t>3042248; 3110167</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3055452; 3122071</t>
+          <t>3056925; 3121659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3293620; 3348714</t>
+          <t>3292393; 3353797</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3284043; 3342862</t>
+          <t>3280832; 3341743</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6033195; 6125749</t>
+          <t>6039299; 6126045</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6407334; 6499895</t>
+          <t>6407585; 6497022</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6350672; 6437806</t>
+          <t>6352029; 6437817</t>
         </is>
       </c>
     </row>
